--- a/public/Soltronic_Product_Master_Clean_12AUG.xlsx
+++ b/public/Soltronic_Product_Master_Clean_12AUG.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\soltronic-website\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC8E4915-AEC0-4422-A738-7F6A20D0BB82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BF6A863-66EF-4557-80D4-40458F19FB18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -784,7 +784,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -821,9 +821,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1154,7 +1151,7 @@
       <c r="J2" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="K2" s="13" t="s">
+      <c r="K2" s="8" t="s">
         <v>144</v>
       </c>
     </row>
@@ -1189,7 +1186,7 @@
       <c r="J3" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="K3" s="13" t="s">
+      <c r="K3" s="8" t="s">
         <v>144</v>
       </c>
     </row>
@@ -1224,7 +1221,7 @@
       <c r="J4" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="K4" s="13" t="s">
+      <c r="K4" s="8" t="s">
         <v>144</v>
       </c>
     </row>
@@ -1259,7 +1256,7 @@
       <c r="J5" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="K5" s="13" t="s">
+      <c r="K5" s="8" t="s">
         <v>144</v>
       </c>
     </row>
@@ -1294,7 +1291,7 @@
       <c r="J6" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="K6" s="13" t="s">
+      <c r="K6" s="8" t="s">
         <v>144</v>
       </c>
     </row>
@@ -1329,7 +1326,7 @@
       <c r="J7" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="K7" s="13" t="s">
+      <c r="K7" s="8" t="s">
         <v>144</v>
       </c>
     </row>
@@ -1364,7 +1361,7 @@
       <c r="J8" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="K8" s="13" t="s">
+      <c r="K8" s="8" t="s">
         <v>144</v>
       </c>
     </row>
@@ -1399,7 +1396,7 @@
       <c r="J9" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="K9" s="13" t="s">
+      <c r="K9" s="8" t="s">
         <v>144</v>
       </c>
     </row>
@@ -1434,7 +1431,7 @@
       <c r="J10" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="K10" s="13" t="s">
+      <c r="K10" s="8" t="s">
         <v>144</v>
       </c>
     </row>
@@ -1469,7 +1466,7 @@
       <c r="J11" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="K11" s="13" t="s">
+      <c r="K11" s="8" t="s">
         <v>144</v>
       </c>
     </row>
@@ -1504,7 +1501,7 @@
       <c r="J12" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="K12" s="13" t="s">
+      <c r="K12" s="8" t="s">
         <v>144</v>
       </c>
     </row>
@@ -1539,7 +1536,7 @@
       <c r="J13" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="K13" s="13" t="s">
+      <c r="K13" s="8" t="s">
         <v>144</v>
       </c>
     </row>
@@ -1574,7 +1571,7 @@
       <c r="J14" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="K14" s="13" t="s">
+      <c r="K14" s="8" t="s">
         <v>144</v>
       </c>
     </row>
@@ -1609,7 +1606,7 @@
       <c r="J15" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="K15" s="13" t="s">
+      <c r="K15" s="8" t="s">
         <v>144</v>
       </c>
     </row>
@@ -1644,7 +1641,7 @@
       <c r="J16" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="K16" s="13" t="s">
+      <c r="K16" s="8" t="s">
         <v>144</v>
       </c>
     </row>
@@ -1679,7 +1676,7 @@
       <c r="J17" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="K17" s="13" t="s">
+      <c r="K17" s="8" t="s">
         <v>144</v>
       </c>
     </row>
@@ -1714,7 +1711,7 @@
       <c r="J18" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="K18" s="13" t="s">
+      <c r="K18" s="8" t="s">
         <v>144</v>
       </c>
     </row>
@@ -1749,7 +1746,7 @@
       <c r="J19" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="K19" s="13" t="s">
+      <c r="K19" s="8" t="s">
         <v>144</v>
       </c>
     </row>
@@ -1784,7 +1781,7 @@
       <c r="J20" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="K20" s="13" t="s">
+      <c r="K20" s="8" t="s">
         <v>144</v>
       </c>
     </row>
@@ -1819,7 +1816,7 @@
       <c r="J21" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="K21" s="13" t="s">
+      <c r="K21" s="8" t="s">
         <v>144</v>
       </c>
     </row>
@@ -1854,7 +1851,7 @@
       <c r="J22" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="K22" s="13" t="s">
+      <c r="K22" s="8" t="s">
         <v>144</v>
       </c>
     </row>
@@ -1889,7 +1886,7 @@
       <c r="J23" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="K23" s="13" t="s">
+      <c r="K23" s="8" t="s">
         <v>144</v>
       </c>
     </row>
@@ -1924,7 +1921,7 @@
       <c r="J24" s="5" t="s">
         <v>134</v>
       </c>
-      <c r="K24" s="13" t="s">
+      <c r="K24" s="8" t="s">
         <v>144</v>
       </c>
     </row>
@@ -1959,7 +1956,7 @@
       <c r="J25" s="7" t="s">
         <v>139</v>
       </c>
-      <c r="K25" s="13" t="s">
+      <c r="K25" s="8" t="s">
         <v>144</v>
       </c>
     </row>
